--- a/CHI TIET XA NO NSNN.xlsx
+++ b/CHI TIET XA NO NSNN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WEB BHXHCN\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA1C01B3-C980-45EC-927A-C503420D9556}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8328" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="XÃ CÁI NƯỚC" sheetId="1" r:id="rId1"/>
@@ -21,10 +22,19 @@
     <sheet name="XÃ PHÚ TÂN" sheetId="8" r:id="rId7"/>
     <sheet name="TỔNG HỢP" sheetId="9" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -171,11 +181,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00\ _₫_-;\-* #,##0.00\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0\ _₫_-;\-* #,##0\ _₫_-;_-* &quot;-&quot;??\ _₫_-;_-@_-"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -371,10 +381,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -391,74 +401,73 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -470,7 +479,7 @@
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2 2" xfId="2"/>
+    <cellStyle name="Normal 2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -747,16 +756,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="33" t="s">
         <v>17</v>
       </c>
@@ -769,7 +778,7 @@
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
     </row>
-    <row r="2" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -798,7 +807,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -816,7 +825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -834,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -852,7 +861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -870,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -888,7 +897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -906,7 +915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -924,7 +933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -942,7 +951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -960,7 +969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -978,7 +987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -996,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>12</v>
       </c>
@@ -1014,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>13</v>
       </c>
@@ -1032,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>14</v>
       </c>
@@ -1050,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>15</v>
       </c>
@@ -1068,7 +1077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A18" s="32" t="s">
         <v>14</v>
       </c>
@@ -1098,29 +1107,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="29.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -1149,7 +1158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -1167,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -1185,7 +1194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1203,7 +1212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -1221,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -1239,7 +1248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -1257,7 +1266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -1275,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -1293,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -1311,7 +1320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -1329,7 +1338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>12</v>
       </c>
@@ -1365,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>13</v>
       </c>
@@ -1383,7 +1392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
         <v>14</v>
       </c>
@@ -1413,29 +1422,29 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="28.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -1464,7 +1473,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -1473,7 +1482,9 @@
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="E3" s="11">
+        <v>113850</v>
+      </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -1482,7 +1493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -1491,7 +1502,9 @@
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="E4" s="11">
+        <v>17419050</v>
+      </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -1500,7 +1513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1509,7 +1522,9 @@
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="11">
+        <v>29828700</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -1518,7 +1533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -1527,7 +1542,9 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>6034050</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -1536,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -1545,7 +1562,9 @@
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="E7" s="11">
+        <v>227700</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1554,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -1563,7 +1582,9 @@
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="E8" s="8">
+        <v>37001250</v>
+      </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
@@ -1572,7 +1593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -1581,7 +1602,9 @@
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="E9" s="8">
+        <v>127398150</v>
+      </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -1590,7 +1613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -1599,7 +1622,9 @@
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="9">
+        <v>59885100</v>
+      </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
@@ -1608,7 +1633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -1617,7 +1642,9 @@
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="E11" s="9">
+        <v>4440150</v>
+      </c>
       <c r="F11" s="9"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
@@ -1626,7 +1653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -1635,7 +1662,9 @@
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="E12" s="9">
+        <v>2618550</v>
+      </c>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
@@ -1644,7 +1673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -1653,7 +1682,9 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9">
+        <v>0</v>
+      </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
@@ -1662,7 +1693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>12</v>
       </c>
@@ -1671,7 +1702,9 @@
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="E14" s="9">
+        <v>6489450</v>
+      </c>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -1680,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>13</v>
       </c>
@@ -1689,7 +1722,9 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="E15" s="9">
+        <v>31536450</v>
+      </c>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
@@ -1698,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
         <v>14</v>
       </c>
@@ -1708,7 +1743,10 @@
         <v>0</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
+      <c r="E16" s="14">
+        <f>SUM(E3:E15)</f>
+        <v>322992450</v>
+      </c>
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="14"/>
@@ -1727,29 +1765,29 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="28.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -1778,7 +1816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -1796,7 +1834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -1814,7 +1852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -1832,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -1850,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -1868,7 +1906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -1886,7 +1924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -1904,7 +1942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -1922,7 +1960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -1940,7 +1978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -1958,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>11</v>
       </c>
@@ -1976,7 +2014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>12</v>
       </c>
@@ -1994,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>13</v>
       </c>
@@ -2012,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
         <v>14</v>
       </c>
@@ -2041,30 +2079,30 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:12" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:12" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -2093,7 +2131,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2102,7 +2140,9 @@
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="E3" s="11">
+        <v>0</v>
+      </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -2111,7 +2151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -2120,7 +2160,9 @@
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="E4" s="11">
+        <v>16508250</v>
+      </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
@@ -2129,7 +2171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -2138,7 +2180,9 @@
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="E5" s="11">
+        <v>19012950</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
@@ -2147,7 +2191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -2156,7 +2200,9 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>3643200</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -2165,7 +2211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -2174,7 +2220,9 @@
       </c>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="E7" s="18">
+        <v>0</v>
+      </c>
       <c r="F7" s="18"/>
       <c r="G7" s="18"/>
       <c r="H7" s="18"/>
@@ -2183,7 +2231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -2192,7 +2240,9 @@
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="E8" s="11">
+        <v>12637350</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -2203,7 +2253,7 @@
       <c r="K8" s="21"/>
       <c r="L8" s="18"/>
     </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -2212,7 +2262,9 @@
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="E9" s="11">
+        <v>62731350</v>
+      </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -2223,7 +2275,7 @@
       <c r="K9" s="21"/>
       <c r="L9" s="18"/>
     </row>
-    <row r="10" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -2232,7 +2284,9 @@
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
+      <c r="E10" s="11">
+        <v>25502400</v>
+      </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
@@ -2243,7 +2297,7 @@
       <c r="K10" s="21"/>
       <c r="L10" s="18"/>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -2252,7 +2306,9 @@
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
+      <c r="E11" s="11">
+        <v>5578650</v>
+      </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
@@ -2263,14 +2319,16 @@
       <c r="K11" s="22"/>
       <c r="L11" s="18"/>
     </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
+      <c r="E12" s="11">
+        <v>6717150</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
@@ -2281,7 +2339,7 @@
       <c r="K12" s="21"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
         <v>14</v>
       </c>
@@ -2291,7 +2349,10 @@
         <v>0</v>
       </c>
       <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14">
+        <f>SUM(E3:E12)</f>
+        <v>152331300</v>
+      </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
@@ -2299,7 +2360,7 @@
         <f>SUM(I4:I12)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="18"/>
     </row>
   </sheetData>
@@ -2313,30 +2374,30 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="16.77734375" customWidth="1"/>
-    <col min="12" max="12" width="14.88671875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="16.81640625" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:12" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:12" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -2365,7 +2426,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2383,7 +2444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -2401,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -2419,7 +2480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -2437,7 +2498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -2455,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -2475,7 +2536,7 @@
       <c r="K8" s="21"/>
       <c r="L8" s="18"/>
     </row>
-    <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -2495,7 +2556,7 @@
       <c r="K9" s="21"/>
       <c r="L9" s="18"/>
     </row>
-    <row r="10" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -2515,7 +2576,7 @@
       <c r="K10" s="21"/>
       <c r="L10" s="18"/>
     </row>
-    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -2535,7 +2596,7 @@
       <c r="K11" s="22"/>
       <c r="L11" s="18"/>
     </row>
-    <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10"/>
       <c r="B12" s="5" t="s">
         <v>13</v>
@@ -2553,7 +2614,7 @@
       <c r="K12" s="21"/>
       <c r="L12" s="16"/>
     </row>
-    <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="15" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
         <v>14</v>
       </c>
@@ -2571,7 +2632,7 @@
         <f>SUM(I4:I12)</f>
         <v>0</v>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="21"/>
       <c r="L13" s="18"/>
     </row>
   </sheetData>
@@ -2585,29 +2646,29 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="33.21875" customWidth="1"/>
-    <col min="3" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="14.5546875" customWidth="1"/>
+    <col min="2" max="2" width="33.1796875" customWidth="1"/>
+    <col min="3" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="25.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9" ht="24.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>15</v>
       </c>
@@ -2636,7 +2697,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="28" x14ac:dyDescent="0.35">
       <c r="A3" s="10">
         <v>1</v>
       </c>
@@ -2647,7 +2708,9 @@
       <c r="D3" s="11">
         <v>0</v>
       </c>
-      <c r="E3" s="11"/>
+      <c r="E3" s="11">
+        <v>0</v>
+      </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -2656,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>2</v>
       </c>
@@ -2667,16 +2730,18 @@
       <c r="D4" s="11">
         <v>11612700</v>
       </c>
-      <c r="E4" s="11"/>
+      <c r="E4" s="11">
+        <v>11612700</v>
+      </c>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12">
         <f t="shared" ref="I4:I13" si="0">C4+D4+E4+F4+G4+H4</f>
-        <v>11612700</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+        <v>23225400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -2687,16 +2752,18 @@
       <c r="D5" s="11">
         <v>16166700</v>
       </c>
-      <c r="E5" s="11"/>
+      <c r="E5" s="11">
+        <v>16052850</v>
+      </c>
       <c r="F5" s="11"/>
       <c r="G5" s="11"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12">
         <f t="shared" si="0"/>
-        <v>16166700</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+        <v>32219550</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>4</v>
       </c>
@@ -2707,16 +2774,18 @@
       <c r="D6" s="11">
         <v>683100</v>
       </c>
-      <c r="E6" s="11"/>
+      <c r="E6" s="11">
+        <v>683100</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12">
         <f t="shared" si="0"/>
-        <v>683100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1366200</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>5</v>
       </c>
@@ -2727,16 +2796,18 @@
       <c r="D7" s="11">
         <v>227700</v>
       </c>
-      <c r="E7" s="11"/>
+      <c r="E7" s="11">
+        <v>227700</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12">
         <f t="shared" si="0"/>
-        <v>227700</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>455400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>6</v>
       </c>
@@ -2747,16 +2818,18 @@
       <c r="D8" s="11">
         <v>35976600</v>
       </c>
-      <c r="E8" s="11"/>
+      <c r="E8" s="11">
+        <v>35976600</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12">
         <f t="shared" si="0"/>
-        <v>35976600</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>71953200</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>7</v>
       </c>
@@ -2767,16 +2840,18 @@
       <c r="D9" s="11">
         <v>71822700</v>
       </c>
-      <c r="E9" s="11"/>
+      <c r="E9" s="11">
+        <v>75482550</v>
+      </c>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12">
         <f t="shared" si="0"/>
-        <v>71822700</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>147305250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>8</v>
       </c>
@@ -2787,16 +2862,18 @@
       <c r="D10" s="11">
         <v>29487150</v>
       </c>
-      <c r="E10" s="11"/>
+      <c r="E10" s="11">
+        <v>29487150</v>
+      </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12">
         <f t="shared" si="0"/>
-        <v>29487150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+        <v>58974300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>9</v>
       </c>
@@ -2807,16 +2884,18 @@
       <c r="D11" s="11">
         <v>2618550</v>
       </c>
-      <c r="E11" s="11"/>
+      <c r="E11" s="11">
+        <v>2618550</v>
+      </c>
       <c r="F11" s="11"/>
       <c r="G11" s="11"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12">
         <f t="shared" si="0"/>
-        <v>2618550</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>5237100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>10</v>
       </c>
@@ -2827,16 +2906,18 @@
       <c r="D12" s="11">
         <v>4781700</v>
       </c>
-      <c r="E12" s="11"/>
+      <c r="E12" s="11">
+        <v>4781700</v>
+      </c>
       <c r="F12" s="11"/>
       <c r="G12" s="11"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12">
         <f t="shared" si="0"/>
-        <v>4781700</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+        <v>9563400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
         <v>14</v>
       </c>
@@ -2849,13 +2930,16 @@
         <f>SUM(D3:D12)</f>
         <v>173376900</v>
       </c>
-      <c r="E13" s="14"/>
+      <c r="E13" s="14">
+        <f>SUM(E3:E12)</f>
+        <v>176922900</v>
+      </c>
       <c r="F13" s="14"/>
       <c r="G13" s="14"/>
       <c r="H13" s="14"/>
       <c r="I13" s="12">
         <f t="shared" si="0"/>
-        <v>173376900</v>
+        <v>350299800</v>
       </c>
     </row>
   </sheetData>
@@ -2869,235 +2953,241 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.21875" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.1796875" customWidth="1"/>
+    <col min="5" max="5" width="16.453125" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" customWidth="1"/>
-    <col min="8" max="8" width="14.109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" customWidth="1"/>
+    <col min="8" max="8" width="14.08984375" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:9" ht="40.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-    </row>
-    <row r="2" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="23" t="s">
         <v>31</v>
       </c>
       <c r="I2" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="27">
-        <v>0</v>
-      </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="28">
+      <c r="C3" s="26">
+        <v>0</v>
+      </c>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="27">
         <f>C3+D3+E3+F3+G3+H3</f>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="24">
         <v>2</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="27">
-        <v>0</v>
-      </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28">
+      <c r="C4" s="26">
+        <v>0</v>
+      </c>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="27">
         <f t="shared" ref="I4:I9" si="0">C4+D4+E4+F4+G4+H4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="24">
         <v>3</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="27">
-        <v>0</v>
-      </c>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
+      <c r="C5" s="26">
+        <v>0</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26">
+        <v>322992450</v>
+      </c>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="27">
+        <f t="shared" si="0"/>
+        <v>322992450</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="24">
         <v>4</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="27">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="29">
+      <c r="C6" s="26">
+        <v>0</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="28">
         <v>5</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="30">
-        <v>0</v>
-      </c>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="29">
+      <c r="C7" s="29">
+        <v>0</v>
+      </c>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29">
+        <v>152331300</v>
+      </c>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="27">
+        <f t="shared" si="0"/>
+        <v>152331300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="28">
         <v>6</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="29">
         <v>0</v>
       </c>
       <c r="D8" s="14">
         <v>173376900</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="28">
-        <f t="shared" si="0"/>
-        <v>173376900</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="29">
+      <c r="E8" s="29">
+        <v>176922900</v>
+      </c>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="27">
+        <f t="shared" si="0"/>
+        <v>350299800</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="28">
         <v>7</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="30">
-        <v>0</v>
-      </c>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="35"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="31">
+      <c r="C9" s="29">
+        <v>0</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="34"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="30">
         <f>SUM(C3:C9)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f t="shared" ref="D10:H10" si="1">SUM(D3:D9)</f>
         <v>173376900</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="F10" s="31">
+        <v>652246650</v>
+      </c>
+      <c r="F10" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="31">
+      <c r="H10" s="30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <f>SUM(I3:I9)</f>
-        <v>173376900</v>
+        <v>825623550</v>
       </c>
     </row>
   </sheetData>
